--- a/backend/uploads/drawings/69aa8af0ff0503c3e2a7cb2a/steel_Transmittal.xlsx
+++ b/backend/uploads/drawings/69aa8af0ff0503c3e2a7cb2a/steel_Transmittal.xlsx
@@ -11,18 +11,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="107">
   <si>
     <t>PROJECT NAME : STEEL</t>
   </si>
   <si>
-    <t>TRANSMITTAL NO: TR-022</t>
+    <t>TRANSMITTAL NO: TR-023</t>
   </si>
   <si>
     <t>FABRICATOR   : INFRA</t>
   </si>
   <si>
-    <t>DATE: 03/10/2026</t>
+    <t>DATE: 03/12/2026</t>
   </si>
   <si>
     <t>Sl. No.</t>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2897,6 +2897,26 @@
         <v>80</v>
       </c>
     </row>
+    <row r="115" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="5">
+        <v>101</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A8:C8"/>
